--- a/data/trans_bre/P1409-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P1409-Provincia-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,24</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 5,0</t>
+          <t>-1,69; 4,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 3,26</t>
+          <t>-3,12; 3,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 2,86</t>
+          <t>-3,08; 2,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-44,25; 355,07</t>
+          <t>-48,89; 312,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-60,37; 176,68</t>
+          <t>-61,67; 181,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-71,08; 144,13</t>
+          <t>-55,31; 173,5</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-0,24</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-5,04%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 4,37</t>
+          <t>0,42; 4,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,13</t>
+          <t>0,48; 4,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 2,52</t>
+          <t>-3,09; 2,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,53; 752,53</t>
+          <t>5,53; 844,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,85; 661,42</t>
+          <t>5,31; 697,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-51,97; 96,83</t>
+          <t>-46,76; 100,83</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 2,64</t>
+          <t>-1,86; 2,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 4,71</t>
+          <t>-1,06; 4,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 3,92</t>
+          <t>-2,34; 3,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-71,77; 361,58</t>
+          <t>-69,73; 335,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-40,91; 508,58</t>
+          <t>-50,68; 434,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-36,24; 134,04</t>
+          <t>-39,07; 101,67</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12,23</t>
+          <t>-1,46</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>317,11%</t>
+          <t>-43,16%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 2,37</t>
+          <t>-1,75; 2,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 4,08</t>
+          <t>-2,14; 3,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 44,64</t>
+          <t>-5,75; 0,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-63,65; 261,27</t>
+          <t>-64,89; 229,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-39,71; 161,47</t>
+          <t>-37,93; 128,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-71,88; 2217,1</t>
+          <t>-82,26; 46,56</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,19</t>
+          <t>2,75</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>166,11%</t>
+          <t>160,72%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 3,34</t>
+          <t>-2,67; 3,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 3,71</t>
+          <t>-2,52; 3,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,15; 6,88</t>
+          <t>0,01; 5,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-79,78; 407,32</t>
+          <t>-75,21; 391,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-66,95; 346,85</t>
+          <t>-63,31; 331,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,24; 962,84</t>
+          <t>-22,73; 1365,38</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1,87</t>
+          <t>1,84</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>51,96%</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 3,32</t>
+          <t>-1,91; 3,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 4,39</t>
+          <t>-0,42; 4,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 4,89</t>
+          <t>-0,8; 4,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-62,15; 291,32</t>
+          <t>-58,01; 276,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-45,65; 989,82</t>
+          <t>-55,59; 909,9</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-26,99; 204,23</t>
+          <t>-19,29; 195,09</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,98</t>
+          <t>3,81</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>94,76%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 2,25</t>
+          <t>-1,01; 2,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 3,51</t>
+          <t>-0,9; 3,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 4,96</t>
+          <t>1,1; 6,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-49,67; 272,26</t>
+          <t>-48,82; 236,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-26,07; 177,45</t>
+          <t>-25,28; 154,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-36,06; 187,26</t>
+          <t>16,06; 233,88</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,71</t>
+          <t>-0,33</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>-8,21%</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 2,11</t>
+          <t>-1,17; 1,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,16; 4,01</t>
+          <t>0,18; 3,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 3,35</t>
+          <t>-2,32; 1,53</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-38,18; 153,14</t>
+          <t>-41,84; 138,3</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 198,16</t>
+          <t>0,74; 209,38</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-27,31; 182,86</t>
+          <t>-44,14; 56,95</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,59</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>23,73%</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,6</t>
+          <t>0,1; 1,64</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,28</t>
+          <t>0,64; 2,33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,4; 9,9</t>
+          <t>-0,1; 1,84</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,37; 98,72</t>
+          <t>3,94; 102,42</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>20,26; 102,86</t>
+          <t>20,53; 112,75</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,06; 282,19</t>
+          <t>-2,36; 53,82</t>
         </is>
       </c>
     </row>
